--- a/Thesis/Evaluation.xlsx
+++ b/Thesis/Evaluation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan\Documents\Coding\Python\Bachelor\Thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FHTechnikum\Semester 5\ReinforcementLearning\Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC09D833-4276-47E9-BB7C-875EB017BCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89A0606-6A11-4619-9774-FC5BD23E9647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D4B319D3-4CDC-4AA8-90B4-403CDF3E49C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4B319D3-4CDC-4AA8-90B4-403CDF3E49C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -2318,7 +2318,7 @@
                   <c:v>25115.942279899915</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>53723.03923609983</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="0.000000000000">
                   <c:v>0</c:v>
@@ -19448,24 +19448,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E2CF9C-842D-4575-AB2D-33AA7D99E5F5}">
   <dimension ref="B2:M249"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="1"/>
-    <col min="2" max="2" width="24.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.54296875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.26953125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.81640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.81640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.1796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.26953125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.453125" style="1"/>
+    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.28515625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>3</v>
       </c>
@@ -19562,7 +19562,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>4</v>
       </c>
@@ -19596,12 +19596,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>15</v>
       </c>
@@ -19624,7 +19624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
@@ -19649,7 +19649,7 @@
         <v>0.11538461538461542</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>0.4071138106758635</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
@@ -19699,12 +19699,12 @@
         <v>-6.7063381373004827E-2</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
@@ -19721,7 +19721,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>8</v>
       </c>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
@@ -19790,17 +19790,17 @@
       </c>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C69" s="1" t="s">
         <v>15</v>
       </c>
@@ -19829,7 +19829,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C70" s="4">
         <v>2</v>
       </c>
@@ -19862,7 +19862,7 @@
         <v>1.2298870855631603E-3</v>
       </c>
     </row>
-    <row r="71" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C71" s="4">
         <v>3</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>0.59741749674809685</v>
       </c>
     </row>
-    <row r="72" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C72" s="4">
         <v>4</v>
       </c>
@@ -19928,12 +19928,12 @@
         <v>2.1779598158572324</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>15</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C76" s="4">
         <v>2</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>2.8452637999706668E-3</v>
       </c>
     </row>
-    <row r="77" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C77" s="4">
         <v>3</v>
       </c>
@@ -20028,7 +20028,7 @@
         <v>0.98557908869580035</v>
       </c>
     </row>
-    <row r="78" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C78" s="4">
         <v>4</v>
       </c>
@@ -20061,12 +20061,12 @@
         <v>8.4402101698002738</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>15</v>
       </c>
@@ -20095,7 +20095,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="82" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C82" s="4">
         <v>2</v>
       </c>
@@ -20128,7 +20128,7 @@
         <v>3.3468187108899664E-3</v>
       </c>
     </row>
-    <row r="83" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C83" s="4">
         <v>3</v>
       </c>
@@ -20161,7 +20161,7 @@
         <v>1.3635981157454051</v>
       </c>
     </row>
-    <row r="84" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C84" s="4">
         <v>4</v>
       </c>
@@ -20194,12 +20194,12 @@
         <v>17.750816016642208</v>
       </c>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
         <v>15</v>
       </c>
@@ -20228,7 +20228,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C88" s="4">
         <v>2</v>
       </c>
@@ -20261,7 +20261,7 @@
         <v>4.139114707381617E-3</v>
       </c>
     </row>
-    <row r="89" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C89" s="4">
         <v>3</v>
       </c>
@@ -20294,37 +20294,45 @@
         <v>2.3141657929178656</v>
       </c>
     </row>
-    <row r="90" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C90" s="4">
         <v>4</v>
       </c>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
+      <c r="D90" s="6">
+        <v>1461.13458299997</v>
+      </c>
+      <c r="E90" s="6">
+        <v>29.6458604999934</v>
+      </c>
+      <c r="F90" s="6">
+        <v>164.796686799963</v>
+      </c>
+      <c r="G90" s="6">
+        <v>52067.462105799903</v>
+      </c>
       <c r="H90" s="6">
         <f>SUM(D90:G90)</f>
-        <v>0</v>
+        <v>53723.03923609983</v>
       </c>
       <c r="I90" s="6">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1490.7804434999634</v>
       </c>
       <c r="J90" s="9">
         <f t="shared" ref="J90" si="17">G90+F90</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="11" t="e">
+        <v>52232.258792599867</v>
+      </c>
+      <c r="K90" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>35.747739736169763</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>15</v>
       </c>
@@ -20353,7 +20361,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C94" s="4">
         <v>2</v>
       </c>
@@ -20386,7 +20394,7 @@
         <v>5.3875266675708243E-3</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C95" s="4">
         <v>3</v>
       </c>
@@ -20419,7 +20427,7 @@
         <v>3.1864320607425864</v>
       </c>
     </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C96" s="4">
         <v>4</v>
       </c>
@@ -20444,7 +20452,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -20455,7 +20463,7 @@
       <c r="J97" s="9"/>
       <c r="K97" s="11"/>
     </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C98" s="4" t="s">
         <v>123</v>
       </c>
@@ -20467,7 +20475,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
         <v>119</v>
       </c>
@@ -20496,7 +20504,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
         <v>25</v>
       </c>
@@ -20529,7 +20537,7 @@
         <v>1.2298870855631603E-3</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C101" s="1" t="s">
         <v>8</v>
       </c>
@@ -20562,7 +20570,7 @@
         <v>2.8452637999706668E-3</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C102" s="1" t="s">
         <v>120</v>
       </c>
@@ -20595,7 +20603,7 @@
         <v>3.3468187108899664E-3</v>
       </c>
     </row>
-    <row r="103" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C103" s="1" t="s">
         <v>121</v>
       </c>
@@ -20628,7 +20636,7 @@
         <v>4.139114707381617E-3</v>
       </c>
     </row>
-    <row r="104" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C104" s="1" t="s">
         <v>122</v>
       </c>
@@ -20661,7 +20669,7 @@
         <v>5.3875266675708243E-3</v>
       </c>
     </row>
-    <row r="105" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -20671,7 +20679,7 @@
       <c r="J105" s="9"/>
       <c r="K105" s="11"/>
     </row>
-    <row r="106" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C106" s="4" t="s">
         <v>160</v>
       </c>
@@ -20683,7 +20691,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C107" s="1" t="s">
         <v>119</v>
       </c>
@@ -20712,7 +20720,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C108" s="1" t="s">
         <v>25</v>
       </c>
@@ -20745,7 +20753,7 @@
         <v>0.59741749674809685</v>
       </c>
     </row>
-    <row r="109" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C109" s="1" t="s">
         <v>8</v>
       </c>
@@ -20774,7 +20782,7 @@
         <v>0.98557908869580035</v>
       </c>
     </row>
-    <row r="110" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C110" s="1" t="s">
         <v>120</v>
       </c>
@@ -20803,7 +20811,7 @@
         <v>1.3635981157454051</v>
       </c>
     </row>
-    <row r="111" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C111" s="1" t="s">
         <v>121</v>
       </c>
@@ -20836,7 +20844,7 @@
         <v>2.3141657929178656</v>
       </c>
     </row>
-    <row r="112" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C112" s="1" t="s">
         <v>122</v>
       </c>
@@ -20869,7 +20877,7 @@
         <v>3.1864320607425864</v>
       </c>
     </row>
-    <row r="113" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -20879,7 +20887,7 @@
       <c r="J113" s="9"/>
       <c r="K113" s="11"/>
     </row>
-    <row r="114" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C114" s="4" t="s">
         <v>161</v>
       </c>
@@ -20891,7 +20899,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="9"/>
     </row>
-    <row r="115" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C115" s="1" t="s">
         <v>119</v>
       </c>
@@ -20920,7 +20928,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="116" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C116" s="1" t="s">
         <v>25</v>
       </c>
@@ -20949,7 +20957,7 @@
         <v>2.1779598158572324</v>
       </c>
     </row>
-    <row r="117" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C117" s="1" t="s">
         <v>8</v>
       </c>
@@ -20978,7 +20986,7 @@
         <v>8.4402101698002738</v>
       </c>
     </row>
-    <row r="118" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C118" s="1" t="s">
         <v>120</v>
       </c>
@@ -21007,20 +21015,40 @@
         <v>17.750816016642208</v>
       </c>
     </row>
-    <row r="119" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C119" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="9"/>
-      <c r="K119" s="11"/>
+      <c r="D119" s="6">
+        <v>1461.13458299997</v>
+      </c>
+      <c r="E119" s="6">
+        <v>29.6458604999934</v>
+      </c>
+      <c r="F119" s="6">
+        <v>164.796686799963</v>
+      </c>
+      <c r="G119" s="6">
+        <v>52067.462105799903</v>
+      </c>
+      <c r="H119" s="6">
+        <f>SUM(D119:G119)</f>
+        <v>53723.03923609983</v>
+      </c>
+      <c r="I119" s="6">
+        <f t="shared" ref="I119" si="29">(D119+E119)</f>
+        <v>1490.7804434999634</v>
+      </c>
+      <c r="J119" s="9">
+        <f t="shared" ref="J119" si="30">G119+F119</f>
+        <v>52232.258792599867</v>
+      </c>
+      <c r="K119" s="11">
+        <f t="shared" ref="K119" si="31">J119/D119</f>
+        <v>35.747739736169763</v>
+      </c>
     </row>
-    <row r="120" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C120" s="1" t="s">
         <v>122</v>
       </c>
@@ -21033,7 +21061,7 @@
       <c r="J120" s="9"/>
       <c r="K120" s="11"/>
     </row>
-    <row r="121" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -21043,7 +21071,7 @@
       <c r="J121" s="9"/>
       <c r="K121" s="11"/>
     </row>
-    <row r="122" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C122" s="4" t="s">
         <v>163</v>
       </c>
@@ -21055,7 +21083,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="9"/>
     </row>
-    <row r="123" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C123" s="1" t="s">
         <v>164</v>
       </c>
@@ -21078,7 +21106,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="9"/>
     </row>
-    <row r="124" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C124" s="1" t="s">
         <v>7</v>
       </c>
@@ -21106,63 +21134,63 @@
       <c r="J124" s="9"/>
       <c r="K124" s="11"/>
     </row>
-    <row r="125" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C125" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="6">
-        <f t="shared" ref="D125:D126" si="29">H71</f>
+        <f t="shared" ref="D125:D126" si="32">H71</f>
         <v>693.49646449999875</v>
       </c>
       <c r="E125" s="11">
-        <f t="shared" ref="E125:E126" si="30">H77</f>
+        <f t="shared" ref="E125:E126" si="33">H77</f>
         <v>867.48310870001933</v>
       </c>
       <c r="F125" s="11">
-        <f t="shared" ref="F125:F126" si="31">H83</f>
+        <f t="shared" ref="F125:F126" si="34">H83</f>
         <v>1042.0707571000091</v>
       </c>
       <c r="G125" s="11">
-        <f t="shared" ref="G125:G126" si="32">H89</f>
+        <f t="shared" ref="G125:G126" si="35">H89</f>
         <v>1191.5927938999666</v>
       </c>
       <c r="H125" s="6">
-        <f t="shared" ref="H125:H126" si="33">H95</f>
+        <f t="shared" ref="H125:H126" si="36">H95</f>
         <v>1488.9312891000236</v>
       </c>
       <c r="I125" s="6"/>
       <c r="J125" s="9"/>
       <c r="K125" s="11"/>
     </row>
-    <row r="126" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>4421.3268159999707</v>
       </c>
       <c r="E126" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>12394.128421799991</v>
       </c>
       <c r="F126" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>25115.942279899915</v>
       </c>
       <c r="G126" s="11">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>53723.03923609983</v>
       </c>
       <c r="H126" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="9"/>
       <c r="K126" s="11"/>
     </row>
-    <row r="127" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="11"/>
       <c r="F127" s="11"/>
@@ -21172,7 +21200,7 @@
       <c r="J127" s="9"/>
       <c r="K127" s="11"/>
     </row>
-    <row r="128" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C128" s="4" t="s">
         <v>170</v>
       </c>
@@ -21184,7 +21212,7 @@
       <c r="J128" s="9"/>
       <c r="K128" s="11"/>
     </row>
-    <row r="129" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C129" s="1" t="s">
         <v>164</v>
       </c>
@@ -21207,7 +21235,7 @@
       <c r="J129" s="9"/>
       <c r="K129" s="11"/>
     </row>
-    <row r="130" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C130" s="1" t="s">
         <v>7</v>
       </c>
@@ -21235,63 +21263,63 @@
       <c r="J130" s="9"/>
       <c r="K130" s="11"/>
     </row>
-    <row r="131" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C131" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="6">
-        <f t="shared" ref="D131:D132" si="34">K71</f>
+        <f t="shared" ref="D131:D132" si="37">K71</f>
         <v>0.59741749674809685</v>
       </c>
       <c r="E131" s="6">
-        <f t="shared" ref="E131:E132" si="35">K77</f>
+        <f t="shared" ref="E131:E132" si="38">K77</f>
         <v>0.98557908869580035</v>
       </c>
       <c r="F131" s="6">
-        <f t="shared" ref="F131:F132" si="36">K83</f>
+        <f t="shared" ref="F131:F132" si="39">K83</f>
         <v>1.3635981157454051</v>
       </c>
       <c r="G131" s="6">
-        <f t="shared" ref="G131:G132" si="37">K89</f>
+        <f t="shared" ref="G131:G132" si="40">K89</f>
         <v>2.3141657929178656</v>
       </c>
       <c r="H131" s="6">
-        <f t="shared" ref="H131:H132" si="38">K95</f>
+        <f t="shared" ref="H131:H132" si="41">K95</f>
         <v>3.1864320607425864</v>
       </c>
       <c r="I131" s="6"/>
       <c r="J131" s="9"/>
       <c r="K131" s="11"/>
     </row>
-    <row r="132" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>2.1779598158572324</v>
       </c>
       <c r="E132" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>8.4402101698002738</v>
       </c>
       <c r="F132" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>17.750816016642208</v>
       </c>
-      <c r="G132" s="6" t="e">
-        <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
+      <c r="G132" s="6">
+        <f t="shared" si="40"/>
+        <v>35.747739736169763</v>
       </c>
       <c r="H132" s="6" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="9"/>
       <c r="K132" s="11"/>
     </row>
-    <row r="133" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="11"/>
       <c r="F133" s="11"/>
@@ -21301,7 +21329,7 @@
       <c r="J133" s="9"/>
       <c r="K133" s="11"/>
     </row>
-    <row r="134" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="11"/>
       <c r="F134" s="11"/>
@@ -21311,7 +21339,7 @@
       <c r="J134" s="9"/>
       <c r="K134" s="11"/>
     </row>
-    <row r="135" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="11"/>
       <c r="F135" s="11"/>
@@ -21321,7 +21349,7 @@
       <c r="J135" s="9"/>
       <c r="K135" s="11"/>
     </row>
-    <row r="136" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="11"/>
       <c r="F136" s="11"/>
@@ -21331,7 +21359,7 @@
       <c r="J136" s="9"/>
       <c r="K136" s="11"/>
     </row>
-    <row r="137" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="11"/>
       <c r="F137" s="11"/>
@@ -21341,7 +21369,7 @@
       <c r="J137" s="9"/>
       <c r="K137" s="11"/>
     </row>
-    <row r="138" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="11"/>
       <c r="F138" s="11"/>
@@ -21351,7 +21379,7 @@
       <c r="J138" s="9"/>
       <c r="K138" s="11"/>
     </row>
-    <row r="139" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="11"/>
       <c r="F139" s="11"/>
@@ -21361,7 +21389,7 @@
       <c r="J139" s="9"/>
       <c r="K139" s="11"/>
     </row>
-    <row r="140" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -21371,7 +21399,7 @@
       <c r="J140" s="9"/>
       <c r="K140" s="11"/>
     </row>
-    <row r="141" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -21381,7 +21409,7 @@
       <c r="J141" s="9"/>
       <c r="K141" s="11"/>
     </row>
-    <row r="142" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -21391,7 +21419,7 @@
       <c r="J142" s="9"/>
       <c r="K142" s="11"/>
     </row>
-    <row r="143" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -21401,7 +21429,7 @@
       <c r="J143" s="9"/>
       <c r="K143" s="11"/>
     </row>
-    <row r="144" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -21411,12 +21439,12 @@
       <c r="J144" s="9"/>
       <c r="K144" s="11"/>
     </row>
-    <row r="146" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C146" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C147" s="1" t="s">
         <v>15</v>
       </c>
@@ -21439,7 +21467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C148" s="4">
         <v>2</v>
       </c>
@@ -21464,7 +21492,7 @@
         <v>-3.5714285714285809E-2</v>
       </c>
     </row>
-    <row r="149" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C149" s="4">
         <v>3</v>
       </c>
@@ -21481,15 +21509,15 @@
         <v>3511</v>
       </c>
       <c r="H149" s="4">
-        <f t="shared" ref="H149:H150" si="39">SUM(F149:G149)</f>
+        <f t="shared" ref="H149:H150" si="42">SUM(F149:G149)</f>
         <v>32129</v>
       </c>
       <c r="I149" s="4">
-        <f t="shared" ref="I149:I150" si="40">1-H149/D149</f>
+        <f t="shared" ref="I149:I150" si="43">1-H149/D149</f>
         <v>0.28371419016832011</v>
       </c>
     </row>
-    <row r="150" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C150" s="4">
         <v>4</v>
       </c>
@@ -21506,20 +21534,20 @@
         <v>4783</v>
       </c>
       <c r="H150" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>649549</v>
       </c>
       <c r="I150" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>2.8896194666582997E-2</v>
       </c>
     </row>
-    <row r="152" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C152" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C153" s="1" t="s">
         <v>15</v>
       </c>
@@ -21542,7 +21570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C154" s="4">
         <v>2</v>
       </c>
@@ -21567,7 +21595,7 @@
         <v>0.1071428571428571</v>
       </c>
     </row>
-    <row r="155" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C155" s="4">
         <v>3</v>
       </c>
@@ -21584,15 +21612,15 @@
         <v>6977</v>
       </c>
       <c r="H155" s="4">
-        <f t="shared" ref="H155:H156" si="41">SUM(F155:G155)</f>
+        <f t="shared" ref="H155:H156" si="44">SUM(F155:G155)</f>
         <v>20937</v>
       </c>
       <c r="I155" s="4">
-        <f t="shared" ref="I155:I156" si="42">1-H155/D155</f>
+        <f t="shared" ref="I155:I156" si="45">1-H155/D155</f>
         <v>0.54540125065138101</v>
       </c>
     </row>
-    <row r="156" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C156" s="4">
         <v>4</v>
       </c>
@@ -21609,20 +21637,20 @@
         <v>9748</v>
       </c>
       <c r="H156" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>630514</v>
       </c>
       <c r="I156" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>5.6591295396327568E-2</v>
       </c>
     </row>
-    <row r="158" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C158" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C159" s="1" t="s">
         <v>15</v>
       </c>
@@ -21645,7 +21673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C160" s="4">
         <v>2</v>
       </c>
@@ -21670,7 +21698,7 @@
         <v>0.1785714285714286</v>
       </c>
     </row>
-    <row r="161" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C161" s="4">
         <v>3</v>
       </c>
@@ -21687,15 +21715,15 @@
         <v>7072</v>
       </c>
       <c r="H161" s="4">
-        <f t="shared" ref="H161:H162" si="43">SUM(F161:G161)</f>
+        <f t="shared" ref="H161:H162" si="46">SUM(F161:G161)</f>
         <v>20716</v>
       </c>
       <c r="I161" s="4">
-        <f t="shared" ref="I161:I162" si="44">1-H161/D161</f>
+        <f t="shared" ref="I161:I162" si="47">1-H161/D161</f>
         <v>0.55197993036181581</v>
       </c>
     </row>
-    <row r="162" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C162" s="4">
         <v>4</v>
       </c>
@@ -21712,20 +21740,20 @@
         <v>9780</v>
       </c>
       <c r="H162" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>631894</v>
       </c>
       <c r="I162" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>5.4662254350479889E-2</v>
       </c>
     </row>
-    <row r="164" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C164" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="165" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C165" s="1" t="s">
         <v>15</v>
       </c>
@@ -21748,7 +21776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C166" s="4">
         <v>2</v>
       </c>
@@ -21773,7 +21801,7 @@
         <v>0.2142857142857143</v>
       </c>
     </row>
-    <row r="167" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C167" s="4">
         <v>3</v>
       </c>
@@ -21790,37 +21818,45 @@
         <v>7065</v>
       </c>
       <c r="H167" s="4">
-        <f t="shared" ref="H167:H168" si="45">SUM(F167:G167)</f>
+        <f t="shared" ref="H167:H168" si="48">SUM(F167:G167)</f>
         <v>20626</v>
       </c>
       <c r="I167" s="4">
-        <f t="shared" ref="I167:I168" si="46">1-H167/D167</f>
+        <f t="shared" ref="I167:I168" si="49">1-H167/D167</f>
         <v>0.5533757741111256</v>
       </c>
     </row>
-    <row r="168" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C168" s="4">
         <v>4</v>
       </c>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
+      <c r="D168" s="4">
+        <v>668432</v>
+      </c>
+      <c r="E168" s="4">
+        <v>669843</v>
+      </c>
+      <c r="F168" s="4">
+        <v>622132</v>
+      </c>
+      <c r="G168" s="4">
+        <v>9791</v>
+      </c>
       <c r="H168" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="I168" s="4" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="48"/>
+        <v>631923</v>
+      </c>
+      <c r="I168" s="4">
+        <f t="shared" si="49"/>
+        <v>5.461886923426762E-2</v>
       </c>
     </row>
-    <row r="170" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C170" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="171" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C171" s="1" t="s">
         <v>15</v>
       </c>
@@ -21843,7 +21879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="172" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C172" s="4">
         <v>2</v>
       </c>
@@ -21868,7 +21904,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="173" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C173" s="4">
         <v>3</v>
       </c>
@@ -21885,15 +21921,15 @@
         <v>7048</v>
       </c>
       <c r="H173" s="4">
-        <f t="shared" ref="H173:H174" si="47">SUM(F173:G173)</f>
+        <f t="shared" ref="H173:H174" si="50">SUM(F173:G173)</f>
         <v>20473</v>
       </c>
       <c r="I173" s="4">
-        <f t="shared" ref="I173:I174" si="48">1-H173/D173</f>
+        <f t="shared" ref="I173:I174" si="51">1-H173/D173</f>
         <v>0.55544698499554856</v>
       </c>
     </row>
-    <row r="174" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C174" s="4">
         <v>4</v>
       </c>
@@ -21902,15 +21938,15 @@
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I174" s="4" t="e">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="175" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -21919,7 +21955,7 @@
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
     </row>
-    <row r="176" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C176" s="4" t="s">
         <v>162</v>
       </c>
@@ -21930,7 +21966,7 @@
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
     </row>
-    <row r="177" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C177" s="4" t="s">
         <v>119</v>
       </c>
@@ -21953,7 +21989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C178" s="4">
         <v>1</v>
       </c>
@@ -21976,7 +22012,7 @@
         <v>-3.5714285714285809E-2</v>
       </c>
     </row>
-    <row r="179" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C179" s="4">
         <v>3</v>
       </c>
@@ -21999,7 +22035,7 @@
         <v>0.1071428571428571</v>
       </c>
     </row>
-    <row r="180" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C180" s="4">
         <v>5</v>
       </c>
@@ -22022,7 +22058,7 @@
         <v>0.1785714285714286</v>
       </c>
     </row>
-    <row r="181" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C181" s="4">
         <v>7</v>
       </c>
@@ -22045,7 +22081,7 @@
         <v>0.2142857142857143</v>
       </c>
     </row>
-    <row r="182" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C182" s="4">
         <v>10</v>
       </c>
@@ -22068,7 +22104,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="183" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -22077,7 +22113,7 @@
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
     </row>
-    <row r="184" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C184" s="4" t="s">
         <v>171</v>
       </c>
@@ -22088,7 +22124,7 @@
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
     </row>
-    <row r="185" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C185" s="4" t="s">
         <v>119</v>
       </c>
@@ -22111,7 +22147,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C186" s="4">
         <v>1</v>
       </c>
@@ -22134,7 +22170,7 @@
         <v>0.28371419016832011</v>
       </c>
     </row>
-    <row r="187" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C187" s="4">
         <v>3</v>
       </c>
@@ -22157,7 +22193,7 @@
         <v>0.54540125065138101</v>
       </c>
     </row>
-    <row r="188" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C188" s="4">
         <v>5</v>
       </c>
@@ -22180,7 +22216,7 @@
         <v>0.55197993036181581</v>
       </c>
     </row>
-    <row r="189" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C189" s="4">
         <v>7</v>
       </c>
@@ -22203,7 +22239,7 @@
         <v>0.5533757741111256</v>
       </c>
     </row>
-    <row r="190" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C190" s="4">
         <v>10</v>
       </c>
@@ -22226,7 +22262,7 @@
         <v>0.55544698499554856</v>
       </c>
     </row>
-    <row r="191" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -22235,7 +22271,7 @@
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
     </row>
-    <row r="192" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -22244,7 +22280,7 @@
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
     </row>
-    <row r="193" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -22253,12 +22289,12 @@
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
     </row>
-    <row r="195" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C195" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="196" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C196" s="1" t="s">
         <v>15</v>
       </c>
@@ -22281,7 +22317,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="197" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C197" s="4">
         <v>2</v>
       </c>
@@ -22306,7 +22342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C198" s="4">
         <v>3</v>
       </c>
@@ -22323,37 +22359,45 @@
         <v>291400</v>
       </c>
       <c r="H198" s="4">
-        <f t="shared" ref="H198:H199" si="49">G198/D198</f>
+        <f t="shared" ref="H198:H199" si="52">G198/D198</f>
         <v>0.36102290649457164</v>
       </c>
       <c r="I198" s="4">
-        <f t="shared" ref="I198:I199" si="50">G198/F198</f>
+        <f t="shared" ref="I198:I199" si="53">G198/F198</f>
         <v>0.56500132816029436</v>
       </c>
     </row>
-    <row r="199" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C199" s="4">
         <v>4</v>
       </c>
-      <c r="D199" s="4"/>
-      <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4" t="e">
-        <f t="shared" si="49"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I199" s="4" t="e">
-        <f t="shared" si="50"/>
-        <v>#DIV/0!</v>
+      <c r="D199" s="4">
+        <v>10723548</v>
+      </c>
+      <c r="E199" s="4">
+        <v>10723548</v>
+      </c>
+      <c r="F199" s="4">
+        <v>10252829</v>
+      </c>
+      <c r="G199" s="4">
+        <v>370719</v>
+      </c>
+      <c r="H199" s="4">
+        <f t="shared" si="52"/>
+        <v>3.4570554447091575E-2</v>
+      </c>
+      <c r="I199" s="4">
+        <f t="shared" si="53"/>
+        <v>3.615772778420473E-2</v>
       </c>
     </row>
-    <row r="201" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C201" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="202" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C202" s="1" t="s">
         <v>15</v>
       </c>
@@ -22376,7 +22420,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="203" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C203" s="4">
         <v>2</v>
       </c>
@@ -22401,7 +22445,7 @@
         <v>0.17012448132780084</v>
       </c>
     </row>
-    <row r="204" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C204" s="4">
         <v>3</v>
       </c>
@@ -22418,37 +22462,45 @@
         <v>565726</v>
       </c>
       <c r="H204" s="4">
-        <f t="shared" ref="H204:H205" si="51">G204/D204</f>
+        <f t="shared" ref="H204:H205" si="54">G204/D204</f>
         <v>0.68855531740612674</v>
       </c>
       <c r="I204" s="4">
-        <f t="shared" ref="I204:I205" si="52">G204/F204</f>
+        <f t="shared" ref="I204:I205" si="55">G204/F204</f>
         <v>2.2108430674477404</v>
       </c>
     </row>
-    <row r="205" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C205" s="4">
         <v>4</v>
       </c>
-      <c r="D205" s="4"/>
-      <c r="E205" s="4"/>
-      <c r="F205" s="4"/>
-      <c r="G205" s="4"/>
-      <c r="H205" s="4" t="e">
-        <f t="shared" si="51"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I205" s="4" t="e">
-        <f t="shared" si="52"/>
-        <v>#DIV/0!</v>
+      <c r="D205" s="4">
+        <v>10697989</v>
+      </c>
+      <c r="E205" s="4">
+        <v>10697989</v>
+      </c>
+      <c r="F205" s="4">
+        <v>9972824</v>
+      </c>
+      <c r="G205" s="4">
+        <v>725166</v>
+      </c>
+      <c r="H205" s="4">
+        <f t="shared" si="54"/>
+        <v>6.7785263192923453E-2</v>
+      </c>
+      <c r="I205" s="4">
+        <f t="shared" si="55"/>
+        <v>7.2714208132019578E-2</v>
       </c>
     </row>
-    <row r="207" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C207" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="208" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C208" s="1" t="s">
         <v>15</v>
       </c>
@@ -22471,7 +22523,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="209" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C209" s="4">
         <v>2</v>
       </c>
@@ -22496,7 +22548,7 @@
         <v>0.42749999999999999</v>
       </c>
     </row>
-    <row r="210" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C210" s="4">
         <v>3</v>
       </c>
@@ -22513,37 +22565,45 @@
         <v>574818</v>
       </c>
       <c r="H210" s="4">
-        <f t="shared" ref="H210:H211" si="53">G210/D210</f>
+        <f t="shared" ref="H210:H211" si="56">G210/D210</f>
         <v>0.69644012474465877</v>
       </c>
       <c r="I210" s="4">
-        <f t="shared" ref="I210:I211" si="54">G210/F210</f>
+        <f t="shared" ref="I210:I211" si="57">G210/F210</f>
         <v>2.2942430193016907</v>
       </c>
     </row>
-    <row r="211" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C211" s="4">
         <v>4</v>
       </c>
-      <c r="D211" s="4"/>
-      <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
-      <c r="H211" s="4" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I211" s="4" t="e">
-        <f t="shared" si="54"/>
-        <v>#DIV/0!</v>
+      <c r="D211" s="4">
+        <v>10721289</v>
+      </c>
+      <c r="E211" s="4">
+        <v>10721289</v>
+      </c>
+      <c r="F211" s="4">
+        <v>9994426</v>
+      </c>
+      <c r="G211" s="4">
+        <v>726863</v>
+      </c>
+      <c r="H211" s="4">
+        <f t="shared" si="56"/>
+        <v>6.7796232337361678E-2</v>
+      </c>
+      <c r="I211" s="4">
+        <f t="shared" si="57"/>
+        <v>7.2726837939467465E-2</v>
       </c>
     </row>
-    <row r="213" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C213" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="214" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C214" s="1" t="s">
         <v>15</v>
       </c>
@@ -22566,7 +22626,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="215" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C215" s="4">
         <v>2</v>
       </c>
@@ -22591,7 +22651,7 @@
         <v>0.54617414248021112</v>
       </c>
     </row>
-    <row r="216" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C216" s="4">
         <v>3</v>
       </c>
@@ -22608,37 +22668,45 @@
         <v>575263</v>
       </c>
       <c r="H216" s="4">
-        <f t="shared" ref="H216:H217" si="55">G216/D216</f>
+        <f t="shared" ref="H216:H217" si="58">G216/D216</f>
         <v>0.69771641758460345</v>
       </c>
       <c r="I216" s="4">
-        <f t="shared" ref="I216:I217" si="56">G216/F216</f>
+        <f t="shared" ref="I216:I217" si="59">G216/F216</f>
         <v>2.3081518751680168</v>
       </c>
     </row>
-    <row r="217" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C217" s="4">
         <v>4</v>
       </c>
-      <c r="D217" s="4"/>
-      <c r="E217" s="4"/>
-      <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="4" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I217" s="4" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
+      <c r="D217" s="4">
+        <v>10722481</v>
+      </c>
+      <c r="E217" s="4">
+        <v>10722481</v>
+      </c>
+      <c r="F217" s="4">
+        <v>9994514</v>
+      </c>
+      <c r="G217" s="4">
+        <v>727967</v>
+      </c>
+      <c r="H217" s="4">
+        <f t="shared" si="58"/>
+        <v>6.7891656790998275E-2</v>
+      </c>
+      <c r="I217" s="4">
+        <f t="shared" si="59"/>
+        <v>7.2836658190683412E-2</v>
       </c>
     </row>
-    <row r="219" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C219" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="220" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C220" s="1" t="s">
         <v>15</v>
       </c>
@@ -22661,7 +22729,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="221" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C221" s="4">
         <v>2</v>
       </c>
@@ -22686,7 +22754,7 @@
         <v>0.58689458689458684</v>
       </c>
     </row>
-    <row r="222" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C222" s="4">
         <v>3</v>
       </c>
@@ -22703,15 +22771,15 @@
         <v>574553</v>
       </c>
       <c r="H222" s="4">
-        <f t="shared" ref="H222:H223" si="57">G222/D222</f>
+        <f t="shared" ref="H222:H223" si="60">G222/D222</f>
         <v>0.69953636401269159</v>
       </c>
       <c r="I222" s="4">
-        <f t="shared" ref="I222:I223" si="58">G222/F222</f>
+        <f t="shared" ref="I222:I223" si="61">G222/F222</f>
         <v>2.3281897714978057</v>
       </c>
     </row>
-    <row r="223" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C223" s="4">
         <v>4</v>
       </c>
@@ -22720,20 +22788,20 @@
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I223" s="4" t="e">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C225" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="226" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C226" s="1" t="s">
         <v>119</v>
       </c>
@@ -22756,7 +22824,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="227" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C227" s="1" t="s">
         <v>25</v>
       </c>
@@ -22779,7 +22847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C228" s="1" t="s">
         <v>8</v>
       </c>
@@ -22802,7 +22870,7 @@
         <v>0.17012448132780084</v>
       </c>
     </row>
-    <row r="229" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C229" s="1" t="s">
         <v>120</v>
       </c>
@@ -22825,7 +22893,7 @@
         <v>0.42749999999999999</v>
       </c>
     </row>
-    <row r="230" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C230" s="1" t="s">
         <v>121</v>
       </c>
@@ -22848,7 +22916,7 @@
         <v>0.54617414248021112</v>
       </c>
     </row>
-    <row r="231" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C231" s="1" t="s">
         <v>122</v>
       </c>
@@ -22871,12 +22939,12 @@
         <v>0.58689458689458684</v>
       </c>
     </row>
-    <row r="234" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C234" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="235" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C235" s="1" t="s">
         <v>119</v>
       </c>
@@ -22899,7 +22967,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="236" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C236" s="1" t="s">
         <v>25</v>
       </c>
@@ -22922,7 +22990,7 @@
         <v>0.56500132816029436</v>
       </c>
     </row>
-    <row r="237" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C237" s="1" t="s">
         <v>8</v>
       </c>
@@ -22945,7 +23013,7 @@
         <v>2.2108430674477404</v>
       </c>
     </row>
-    <row r="238" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C238" s="1" t="s">
         <v>120</v>
       </c>
@@ -22968,7 +23036,7 @@
         <v>2.2942430193016907</v>
       </c>
     </row>
-    <row r="239" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C239" s="1" t="s">
         <v>121</v>
       </c>
@@ -22991,7 +23059,7 @@
         <v>2.3081518751680168</v>
       </c>
     </row>
-    <row r="240" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C240" s="1" t="s">
         <v>122</v>
       </c>
@@ -23014,12 +23082,12 @@
         <v>2.3281897714978057</v>
       </c>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C245" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C246" s="1" t="s">
         <v>164</v>
       </c>
@@ -23033,17 +23101,17 @@
         <v>176</v>
       </c>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C247" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C248" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C249" s="1" t="s">
         <v>9</v>
       </c>

--- a/Thesis/Evaluation.xlsx
+++ b/Thesis/Evaluation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FHTechnikum\Semester 5\ReinforcementLearning\Thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan\Documents\Coding\Python\Bachelor\Thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89A0606-6A11-4619-9774-FC5BD23E9647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA52EE0-4A40-49E4-8913-BB42DE32E1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4B319D3-4CDC-4AA8-90B4-403CDF3E49C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D4B319D3-4CDC-4AA8-90B4-403CDF3E49C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -19448,24 +19448,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E2CF9C-842D-4575-AB2D-33AA7D99E5F5}">
   <dimension ref="B2:M249"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1"/>
-    <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.28515625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="11.453125" style="1"/>
+    <col min="2" max="2" width="24.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.81640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.1796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.26953125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="1">
         <v>2</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="1">
         <v>3</v>
       </c>
@@ -19562,7 +19562,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>4</v>
       </c>
@@ -19596,12 +19596,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
         <v>15</v>
       </c>
@@ -19624,7 +19624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
@@ -19649,7 +19649,7 @@
         <v>0.11538461538461542</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>0.4071138106758635</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
@@ -19699,12 +19699,12 @@
         <v>-6.7063381373004827E-2</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
         <v>33</v>
       </c>
@@ -19721,7 +19721,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
         <v>8</v>
       </c>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
@@ -19790,17 +19790,17 @@
       </c>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C68" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C69" s="1" t="s">
         <v>15</v>
       </c>
@@ -19829,7 +19829,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C70" s="4">
         <v>2</v>
       </c>
@@ -19862,7 +19862,7 @@
         <v>1.2298870855631603E-3</v>
       </c>
     </row>
-    <row r="71" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C71" s="4">
         <v>3</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>0.59741749674809685</v>
       </c>
     </row>
-    <row r="72" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C72" s="4">
         <v>4</v>
       </c>
@@ -19928,12 +19928,12 @@
         <v>2.1779598158572324</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C74" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C75" s="1" t="s">
         <v>15</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C76" s="4">
         <v>2</v>
       </c>
@@ -19995,7 +19995,7 @@
         <v>2.8452637999706668E-3</v>
       </c>
     </row>
-    <row r="77" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C77" s="4">
         <v>3</v>
       </c>
@@ -20028,7 +20028,7 @@
         <v>0.98557908869580035</v>
       </c>
     </row>
-    <row r="78" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C78" s="4">
         <v>4</v>
       </c>
@@ -20061,12 +20061,12 @@
         <v>8.4402101698002738</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="C80" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C81" s="1" t="s">
         <v>15</v>
       </c>
@@ -20095,7 +20095,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="82" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C82" s="4">
         <v>2</v>
       </c>
@@ -20128,7 +20128,7 @@
         <v>3.3468187108899664E-3</v>
       </c>
     </row>
-    <row r="83" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C83" s="4">
         <v>3</v>
       </c>
@@ -20161,7 +20161,7 @@
         <v>1.3635981157454051</v>
       </c>
     </row>
-    <row r="84" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C84" s="4">
         <v>4</v>
       </c>
@@ -20194,12 +20194,12 @@
         <v>17.750816016642208</v>
       </c>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C86" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C87" s="1" t="s">
         <v>15</v>
       </c>
@@ -20228,7 +20228,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C88" s="4">
         <v>2</v>
       </c>
@@ -20261,7 +20261,7 @@
         <v>4.139114707381617E-3</v>
       </c>
     </row>
-    <row r="89" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C89" s="4">
         <v>3</v>
       </c>
@@ -20294,7 +20294,7 @@
         <v>2.3141657929178656</v>
       </c>
     </row>
-    <row r="90" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C90" s="4">
         <v>4</v>
       </c>
@@ -20327,12 +20327,12 @@
         <v>35.747739736169763</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C92" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C93" s="1" t="s">
         <v>15</v>
       </c>
@@ -20361,7 +20361,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C94" s="4">
         <v>2</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>5.3875266675708243E-3</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C95" s="4">
         <v>3</v>
       </c>
@@ -20427,7 +20427,7 @@
         <v>3.1864320607425864</v>
       </c>
     </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C96" s="4">
         <v>4</v>
       </c>
@@ -20452,7 +20452,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -20463,7 +20463,7 @@
       <c r="J97" s="9"/>
       <c r="K97" s="11"/>
     </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C98" s="4" t="s">
         <v>123</v>
       </c>
@@ -20475,7 +20475,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C99" s="1" t="s">
         <v>119</v>
       </c>
@@ -20504,7 +20504,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C100" s="1" t="s">
         <v>25</v>
       </c>
@@ -20537,7 +20537,7 @@
         <v>1.2298870855631603E-3</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C101" s="1" t="s">
         <v>8</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>2.8452637999706668E-3</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C102" s="1" t="s">
         <v>120</v>
       </c>
@@ -20603,7 +20603,7 @@
         <v>3.3468187108899664E-3</v>
       </c>
     </row>
-    <row r="103" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C103" s="1" t="s">
         <v>121</v>
       </c>
@@ -20636,7 +20636,7 @@
         <v>4.139114707381617E-3</v>
       </c>
     </row>
-    <row r="104" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C104" s="1" t="s">
         <v>122</v>
       </c>
@@ -20669,7 +20669,7 @@
         <v>5.3875266675708243E-3</v>
       </c>
     </row>
-    <row r="105" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -20679,7 +20679,7 @@
       <c r="J105" s="9"/>
       <c r="K105" s="11"/>
     </row>
-    <row r="106" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C106" s="4" t="s">
         <v>160</v>
       </c>
@@ -20691,7 +20691,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C107" s="1" t="s">
         <v>119</v>
       </c>
@@ -20720,7 +20720,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C108" s="1" t="s">
         <v>25</v>
       </c>
@@ -20753,7 +20753,7 @@
         <v>0.59741749674809685</v>
       </c>
     </row>
-    <row r="109" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C109" s="1" t="s">
         <v>8</v>
       </c>
@@ -20782,7 +20782,7 @@
         <v>0.98557908869580035</v>
       </c>
     </row>
-    <row r="110" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C110" s="1" t="s">
         <v>120</v>
       </c>
@@ -20811,7 +20811,7 @@
         <v>1.3635981157454051</v>
       </c>
     </row>
-    <row r="111" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C111" s="1" t="s">
         <v>121</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>2.3141657929178656</v>
       </c>
     </row>
-    <row r="112" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C112" s="1" t="s">
         <v>122</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>3.1864320607425864</v>
       </c>
     </row>
-    <row r="113" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -20887,7 +20887,7 @@
       <c r="J113" s="9"/>
       <c r="K113" s="11"/>
     </row>
-    <row r="114" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C114" s="4" t="s">
         <v>161</v>
       </c>
@@ -20899,7 +20899,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="9"/>
     </row>
-    <row r="115" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C115" s="1" t="s">
         <v>119</v>
       </c>
@@ -20928,7 +20928,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="116" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C116" s="1" t="s">
         <v>25</v>
       </c>
@@ -20957,7 +20957,7 @@
         <v>2.1779598158572324</v>
       </c>
     </row>
-    <row r="117" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C117" s="1" t="s">
         <v>8</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>8.4402101698002738</v>
       </c>
     </row>
-    <row r="118" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C118" s="1" t="s">
         <v>120</v>
       </c>
@@ -21015,7 +21015,7 @@
         <v>17.750816016642208</v>
       </c>
     </row>
-    <row r="119" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C119" s="1" t="s">
         <v>121</v>
       </c>
@@ -21048,7 +21048,7 @@
         <v>35.747739736169763</v>
       </c>
     </row>
-    <row r="120" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C120" s="1" t="s">
         <v>122</v>
       </c>
@@ -21061,7 +21061,7 @@
       <c r="J120" s="9"/>
       <c r="K120" s="11"/>
     </row>
-    <row r="121" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -21071,7 +21071,7 @@
       <c r="J121" s="9"/>
       <c r="K121" s="11"/>
     </row>
-    <row r="122" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C122" s="4" t="s">
         <v>163</v>
       </c>
@@ -21083,7 +21083,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="9"/>
     </row>
-    <row r="123" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C123" s="1" t="s">
         <v>164</v>
       </c>
@@ -21106,7 +21106,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="9"/>
     </row>
-    <row r="124" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C124" s="1" t="s">
         <v>7</v>
       </c>
@@ -21134,7 +21134,7 @@
       <c r="J124" s="9"/>
       <c r="K124" s="11"/>
     </row>
-    <row r="125" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C125" s="1" t="s">
         <v>8</v>
       </c>
@@ -21162,7 +21162,7 @@
       <c r="J125" s="9"/>
       <c r="K125" s="11"/>
     </row>
-    <row r="126" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C126" s="1" t="s">
         <v>9</v>
       </c>
@@ -21190,7 +21190,7 @@
       <c r="J126" s="9"/>
       <c r="K126" s="11"/>
     </row>
-    <row r="127" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D127" s="6"/>
       <c r="E127" s="11"/>
       <c r="F127" s="11"/>
@@ -21200,7 +21200,7 @@
       <c r="J127" s="9"/>
       <c r="K127" s="11"/>
     </row>
-    <row r="128" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C128" s="4" t="s">
         <v>170</v>
       </c>
@@ -21212,7 +21212,7 @@
       <c r="J128" s="9"/>
       <c r="K128" s="11"/>
     </row>
-    <row r="129" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C129" s="1" t="s">
         <v>164</v>
       </c>
@@ -21235,7 +21235,7 @@
       <c r="J129" s="9"/>
       <c r="K129" s="11"/>
     </row>
-    <row r="130" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C130" s="1" t="s">
         <v>7</v>
       </c>
@@ -21263,7 +21263,7 @@
       <c r="J130" s="9"/>
       <c r="K130" s="11"/>
     </row>
-    <row r="131" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C131" s="1" t="s">
         <v>8</v>
       </c>
@@ -21291,7 +21291,7 @@
       <c r="J131" s="9"/>
       <c r="K131" s="11"/>
     </row>
-    <row r="132" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C132" s="1" t="s">
         <v>9</v>
       </c>
@@ -21319,7 +21319,7 @@
       <c r="J132" s="9"/>
       <c r="K132" s="11"/>
     </row>
-    <row r="133" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D133" s="6"/>
       <c r="E133" s="11"/>
       <c r="F133" s="11"/>
@@ -21329,7 +21329,7 @@
       <c r="J133" s="9"/>
       <c r="K133" s="11"/>
     </row>
-    <row r="134" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D134" s="6"/>
       <c r="E134" s="11"/>
       <c r="F134" s="11"/>
@@ -21339,7 +21339,7 @@
       <c r="J134" s="9"/>
       <c r="K134" s="11"/>
     </row>
-    <row r="135" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D135" s="6"/>
       <c r="E135" s="11"/>
       <c r="F135" s="11"/>
@@ -21349,7 +21349,7 @@
       <c r="J135" s="9"/>
       <c r="K135" s="11"/>
     </row>
-    <row r="136" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D136" s="6"/>
       <c r="E136" s="11"/>
       <c r="F136" s="11"/>
@@ -21359,7 +21359,7 @@
       <c r="J136" s="9"/>
       <c r="K136" s="11"/>
     </row>
-    <row r="137" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D137" s="6"/>
       <c r="E137" s="11"/>
       <c r="F137" s="11"/>
@@ -21369,7 +21369,7 @@
       <c r="J137" s="9"/>
       <c r="K137" s="11"/>
     </row>
-    <row r="138" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D138" s="6"/>
       <c r="E138" s="11"/>
       <c r="F138" s="11"/>
@@ -21379,7 +21379,7 @@
       <c r="J138" s="9"/>
       <c r="K138" s="11"/>
     </row>
-    <row r="139" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D139" s="6"/>
       <c r="E139" s="11"/>
       <c r="F139" s="11"/>
@@ -21389,7 +21389,7 @@
       <c r="J139" s="9"/>
       <c r="K139" s="11"/>
     </row>
-    <row r="140" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -21399,7 +21399,7 @@
       <c r="J140" s="9"/>
       <c r="K140" s="11"/>
     </row>
-    <row r="141" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -21409,7 +21409,7 @@
       <c r="J141" s="9"/>
       <c r="K141" s="11"/>
     </row>
-    <row r="142" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -21419,7 +21419,7 @@
       <c r="J142" s="9"/>
       <c r="K142" s="11"/>
     </row>
-    <row r="143" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -21429,7 +21429,7 @@
       <c r="J143" s="9"/>
       <c r="K143" s="11"/>
     </row>
-    <row r="144" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -21439,12 +21439,12 @@
       <c r="J144" s="9"/>
       <c r="K144" s="11"/>
     </row>
-    <row r="146" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C146" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C147" s="1" t="s">
         <v>15</v>
       </c>
@@ -21467,7 +21467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C148" s="4">
         <v>2</v>
       </c>
@@ -21492,7 +21492,7 @@
         <v>-3.5714285714285809E-2</v>
       </c>
     </row>
-    <row r="149" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C149" s="4">
         <v>3</v>
       </c>
@@ -21517,7 +21517,7 @@
         <v>0.28371419016832011</v>
       </c>
     </row>
-    <row r="150" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C150" s="4">
         <v>4</v>
       </c>
@@ -21542,12 +21542,12 @@
         <v>2.8896194666582997E-2</v>
       </c>
     </row>
-    <row r="152" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C152" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C153" s="1" t="s">
         <v>15</v>
       </c>
@@ -21570,7 +21570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C154" s="4">
         <v>2</v>
       </c>
@@ -21595,7 +21595,7 @@
         <v>0.1071428571428571</v>
       </c>
     </row>
-    <row r="155" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C155" s="4">
         <v>3</v>
       </c>
@@ -21620,7 +21620,7 @@
         <v>0.54540125065138101</v>
       </c>
     </row>
-    <row r="156" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C156" s="4">
         <v>4</v>
       </c>
@@ -21645,12 +21645,12 @@
         <v>5.6591295396327568E-2</v>
       </c>
     </row>
-    <row r="158" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C158" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C159" s="1" t="s">
         <v>15</v>
       </c>
@@ -21673,7 +21673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C160" s="4">
         <v>2</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>0.1785714285714286</v>
       </c>
     </row>
-    <row r="161" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C161" s="4">
         <v>3</v>
       </c>
@@ -21723,7 +21723,7 @@
         <v>0.55197993036181581</v>
       </c>
     </row>
-    <row r="162" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C162" s="4">
         <v>4</v>
       </c>
@@ -21748,12 +21748,12 @@
         <v>5.4662254350479889E-2</v>
       </c>
     </row>
-    <row r="164" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C164" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="165" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C165" s="1" t="s">
         <v>15</v>
       </c>
@@ -21776,7 +21776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C166" s="4">
         <v>2</v>
       </c>
@@ -21801,7 +21801,7 @@
         <v>0.2142857142857143</v>
       </c>
     </row>
-    <row r="167" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C167" s="4">
         <v>3</v>
       </c>
@@ -21826,7 +21826,7 @@
         <v>0.5533757741111256</v>
       </c>
     </row>
-    <row r="168" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C168" s="4">
         <v>4</v>
       </c>
@@ -21851,12 +21851,12 @@
         <v>5.461886923426762E-2</v>
       </c>
     </row>
-    <row r="170" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C170" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="171" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C171" s="1" t="s">
         <v>15</v>
       </c>
@@ -21879,7 +21879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="172" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C172" s="4">
         <v>2</v>
       </c>
@@ -21904,7 +21904,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="173" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C173" s="4">
         <v>3</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>0.55544698499554856</v>
       </c>
     </row>
-    <row r="174" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C174" s="4">
         <v>4</v>
       </c>
@@ -21946,7 +21946,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="175" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -21955,7 +21955,7 @@
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
     </row>
-    <row r="176" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C176" s="4" t="s">
         <v>162</v>
       </c>
@@ -21966,7 +21966,7 @@
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
     </row>
-    <row r="177" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C177" s="4" t="s">
         <v>119</v>
       </c>
@@ -21989,7 +21989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C178" s="4">
         <v>1</v>
       </c>
@@ -22012,7 +22012,7 @@
         <v>-3.5714285714285809E-2</v>
       </c>
     </row>
-    <row r="179" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C179" s="4">
         <v>3</v>
       </c>
@@ -22035,7 +22035,7 @@
         <v>0.1071428571428571</v>
       </c>
     </row>
-    <row r="180" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C180" s="4">
         <v>5</v>
       </c>
@@ -22058,7 +22058,7 @@
         <v>0.1785714285714286</v>
       </c>
     </row>
-    <row r="181" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C181" s="4">
         <v>7</v>
       </c>
@@ -22081,7 +22081,7 @@
         <v>0.2142857142857143</v>
       </c>
     </row>
-    <row r="182" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C182" s="4">
         <v>10</v>
       </c>
@@ -22104,7 +22104,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="183" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -22113,7 +22113,7 @@
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
     </row>
-    <row r="184" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C184" s="4" t="s">
         <v>171</v>
       </c>
@@ -22124,7 +22124,7 @@
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
     </row>
-    <row r="185" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C185" s="4" t="s">
         <v>119</v>
       </c>
@@ -22147,7 +22147,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C186" s="4">
         <v>1</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>0.28371419016832011</v>
       </c>
     </row>
-    <row r="187" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C187" s="4">
         <v>3</v>
       </c>
@@ -22193,7 +22193,7 @@
         <v>0.54540125065138101</v>
       </c>
     </row>
-    <row r="188" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C188" s="4">
         <v>5</v>
       </c>
@@ -22216,7 +22216,7 @@
         <v>0.55197993036181581</v>
       </c>
     </row>
-    <row r="189" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C189" s="4">
         <v>7</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>0.5533757741111256</v>
       </c>
     </row>
-    <row r="190" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C190" s="4">
         <v>10</v>
       </c>
@@ -22262,7 +22262,7 @@
         <v>0.55544698499554856</v>
       </c>
     </row>
-    <row r="191" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -22271,7 +22271,7 @@
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
     </row>
-    <row r="192" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -22280,7 +22280,7 @@
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
     </row>
-    <row r="193" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -22289,12 +22289,12 @@
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
     </row>
-    <row r="195" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C195" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="196" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C196" s="1" t="s">
         <v>15</v>
       </c>
@@ -22317,7 +22317,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="197" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C197" s="4">
         <v>2</v>
       </c>
@@ -22342,7 +22342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C198" s="4">
         <v>3</v>
       </c>
@@ -22367,7 +22367,7 @@
         <v>0.56500132816029436</v>
       </c>
     </row>
-    <row r="199" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C199" s="4">
         <v>4</v>
       </c>
@@ -22392,12 +22392,12 @@
         <v>3.615772778420473E-2</v>
       </c>
     </row>
-    <row r="201" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C201" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="202" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C202" s="1" t="s">
         <v>15</v>
       </c>
@@ -22420,7 +22420,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="203" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C203" s="4">
         <v>2</v>
       </c>
@@ -22445,7 +22445,7 @@
         <v>0.17012448132780084</v>
       </c>
     </row>
-    <row r="204" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C204" s="4">
         <v>3</v>
       </c>
@@ -22470,7 +22470,7 @@
         <v>2.2108430674477404</v>
       </c>
     </row>
-    <row r="205" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C205" s="4">
         <v>4</v>
       </c>
@@ -22495,12 +22495,12 @@
         <v>7.2714208132019578E-2</v>
       </c>
     </row>
-    <row r="207" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C207" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="208" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C208" s="1" t="s">
         <v>15</v>
       </c>
@@ -22523,7 +22523,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="209" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C209" s="4">
         <v>2</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>0.42749999999999999</v>
       </c>
     </row>
-    <row r="210" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C210" s="4">
         <v>3</v>
       </c>
@@ -22573,7 +22573,7 @@
         <v>2.2942430193016907</v>
       </c>
     </row>
-    <row r="211" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C211" s="4">
         <v>4</v>
       </c>
@@ -22598,12 +22598,12 @@
         <v>7.2726837939467465E-2</v>
       </c>
     </row>
-    <row r="213" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C213" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="214" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C214" s="1" t="s">
         <v>15</v>
       </c>
@@ -22626,7 +22626,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="215" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C215" s="4">
         <v>2</v>
       </c>
@@ -22651,7 +22651,7 @@
         <v>0.54617414248021112</v>
       </c>
     </row>
-    <row r="216" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C216" s="4">
         <v>3</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>2.3081518751680168</v>
       </c>
     </row>
-    <row r="217" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C217" s="4">
         <v>4</v>
       </c>
@@ -22701,12 +22701,12 @@
         <v>7.2836658190683412E-2</v>
       </c>
     </row>
-    <row r="219" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C219" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="220" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C220" s="1" t="s">
         <v>15</v>
       </c>
@@ -22729,7 +22729,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="221" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C221" s="4">
         <v>2</v>
       </c>
@@ -22754,7 +22754,7 @@
         <v>0.58689458689458684</v>
       </c>
     </row>
-    <row r="222" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C222" s="4">
         <v>3</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>2.3281897714978057</v>
       </c>
     </row>
-    <row r="223" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C223" s="4">
         <v>4</v>
       </c>
@@ -22796,12 +22796,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C225" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="226" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C226" s="1" t="s">
         <v>119</v>
       </c>
@@ -22824,7 +22824,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="227" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C227" s="1" t="s">
         <v>25</v>
       </c>
@@ -22847,7 +22847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C228" s="1" t="s">
         <v>8</v>
       </c>
@@ -22870,7 +22870,7 @@
         <v>0.17012448132780084</v>
       </c>
     </row>
-    <row r="229" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C229" s="1" t="s">
         <v>120</v>
       </c>
@@ -22893,7 +22893,7 @@
         <v>0.42749999999999999</v>
       </c>
     </row>
-    <row r="230" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C230" s="1" t="s">
         <v>121</v>
       </c>
@@ -22916,7 +22916,7 @@
         <v>0.54617414248021112</v>
       </c>
     </row>
-    <row r="231" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C231" s="1" t="s">
         <v>122</v>
       </c>
@@ -22939,12 +22939,12 @@
         <v>0.58689458689458684</v>
       </c>
     </row>
-    <row r="234" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C234" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="235" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C235" s="1" t="s">
         <v>119</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="236" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C236" s="1" t="s">
         <v>25</v>
       </c>
@@ -22990,7 +22990,7 @@
         <v>0.56500132816029436</v>
       </c>
     </row>
-    <row r="237" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C237" s="1" t="s">
         <v>8</v>
       </c>
@@ -23013,7 +23013,7 @@
         <v>2.2108430674477404</v>
       </c>
     </row>
-    <row r="238" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C238" s="1" t="s">
         <v>120</v>
       </c>
@@ -23036,7 +23036,7 @@
         <v>2.2942430193016907</v>
       </c>
     </row>
-    <row r="239" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C239" s="1" t="s">
         <v>121</v>
       </c>
@@ -23059,7 +23059,7 @@
         <v>2.3081518751680168</v>
       </c>
     </row>
-    <row r="240" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C240" s="1" t="s">
         <v>122</v>
       </c>
@@ -23082,12 +23082,12 @@
         <v>2.3281897714978057</v>
       </c>
     </row>
-    <row r="245" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C245" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="246" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C246" s="1" t="s">
         <v>164</v>
       </c>
@@ -23101,17 +23101,17 @@
         <v>176</v>
       </c>
     </row>
-    <row r="247" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C247" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C248" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C249" s="1" t="s">
         <v>9</v>
       </c>
